--- a/CSV_jira_configuration_file/jira-import-field-mapping.xlsx
+++ b/CSV_jira_configuration_file/jira-import-field-mapping.xlsx
@@ -516,12 +516,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1164,44 +1164,176 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>blocks (OpenProject relation)</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Issue Link — Blocks</t>
+          <t>Comment (via REST API, {panel} macro)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Map via derived column</t>
+          <t>Map — same pass as issue</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>See Derived Columns tab ('blocks'). Requires BOTH sides of the link to already have Jira keys — Pass 5 only</t>
+          <t>Only needs the row's own new key — created same pass as the issue, no dependency on other rows</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>follows (OpenProject relation)</t>
+          <t>attachments (AttachmentPath)</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
+          <t>Attachment (via jira_attach.py)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Map — same pass as issue</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Only needs the row's own new key — folded into Pass 0-4, not a separate final pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>includes</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Issue Link — Includes</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Map via derived column</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Not a Jira default link type — create it, or map to closest existing type (e.g. 'relates to'). Pass 5 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>blocks</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Issue Link — Blocks</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Map via derived column</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Jira system default. Confirm 'requires' isn't just its inverse direction before creating both. Pass 5 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>relates</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Issue Link — Relates</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Map via derived column</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Jira system default ('relates to'). Pass 5 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Issue Link — Duplicates</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Map via derived column</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Jira system default, symmetric (duplicates / is duplicated by). Pass 5 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Issue Link — Follows/Precedes</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Map via derived column</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>See Derived Columns tab ('follows'). Same key-dependency as blocks — Pass 5 only</t>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Usually a custom link type — confirm it exists in your instance before Pass 5. Check against 'blocks/requires' for a possible duplicate pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>requires</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Issue Link — Requires</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Map via derived column</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Check whether this is just the inverse direction of 'blocks' in your export — if so, only import one direction, not both. Pass 5 only</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1352,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1476,14 +1608,14 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Blocks / Follows Link Types (NEW — confirm IDs in your instance)</t>
+          <t>Peer Relation Link Types (Pass 5 — confirm all 6 IDs in your instance)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>OpenProject Relation</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1493,33 +1625,85 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Direction / Notes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Blocks</t>
+          <t>includes</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr"/>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>outward: blocks / inward: is blocked by (Jira system default — confirm ID via Issue Linking admin screen)</t>
+          <t>Not a Jira default — create custom link type, or map to 'relates to'</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Follows / Precedes</t>
+          <t>blocks</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr"/>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>outward: follows / inward: precedes (custom link type in most instances — confirm it exists before Pass 5, create it if not)</t>
+          <t>Jira system default: outward 'blocks' / inward 'is blocked by'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>relates</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr"/>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Jira system default: 'relates to' (symmetric)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Jira system default: 'duplicates' / 'is duplicated by' (symmetric)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr"/>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Usually custom — confirm it exists. Check whether this is just 'blocks'/'requires' reversed before treating as separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>requires</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr"/>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Check whether this is just the inverse direction of 'blocks' in your export — if so, import only one direction</t>
         </is>
       </c>
     </row>
@@ -1538,15 +1722,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1559,7 +1743,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pass 5 (Blocks / Follows) is new — inserted after all hierarchy passes, before attachments, because these links can target ANY issue type including subtasks, so both sides must already have real Jira keys.</t>
+          <t>Comments and attachments ride along with each pass (0-4) — they only need the row's own new key. All 6 peer relations (includes/blocks/relates/duplicates/follows/requires) move to a single final pass, since any of them can target a row from any earlier OR later pass.</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1809,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Export from Jira: Key + op-ticket-legacy → build OP ID→Jira key map</t>
+          <t>Create issues + comments + attachments together. Export from Jira: Key + op-ticket-legacy → build OP ID→Jira key map</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1847,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Export from Jira: Key + op-ticket-legacy → update mapping file</t>
+          <t>Create issues + comments + attachments together. Export: Key + op-ticket-legacy → update mapping file</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1890,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Verify Epic links resolved on import log</t>
+          <t>Create issues + comments + attachments together. Verify Epic links resolved on import log</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1926,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Check import log for unresolved links</t>
+          <t>Comments/attachments for these rows already handled in their origin pass. Check import log for unresolved links</t>
         </is>
       </c>
     </row>
@@ -1779,25 +1963,29 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Verify subtask-parent-id resolved on import log</t>
+          <t>Create issues + comments + attachments together. Verify subtask-parent-id resolved on import log</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Pass 5 (NEW)</t>
+          <t>Pass 5 (relations)</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Any type with blocks/follows relation populated</t>
+          <t>Any type with a peer relation populated</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>blocks
-follows</t>
+          <t>includes
+blocks
+relates
+duplicates
+follows
+requires</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1808,45 +1996,12 @@
       <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Pass 0-4 complete
-ALL rows have real Jira keys, since blocks/follows can target any level incl. subtasks</t>
+ALL rows have real Jira keys — a relation can point to a row created in any pass, including the last</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Confirm Blocks/Follows link type IDs in Lookup Tables tab before running. Check import log for unresolved links (source or target key missing = row skipped, not soft-failed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Pass 6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Rows with AttachmentPath non-blank</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>— run jira_attach.py —</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>All passes complete
-All Jira keys exist</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Review jira_attach_report.csv</t>
+          <t>Confirm all 6 link type IDs in Lookup Tables tab first. Check for blocks/requires and follows/its-inverse duplicate-direction pairs before running. Check import log for unresolved links (missing key = row skipped, not soft-failed)</t>
         </is>
       </c>
     </row>
@@ -1865,14 +2020,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1885,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>All formulas assume: column A = Issue ID, column B = Type, column C = Project, column AB = raw 'parent' reference from source export. New columns AC/AD hold raw blocks/follows references.</t>
+          <t>Columns A=Issue ID, B=Type, C=Project, AB=raw parent reference. New columns AC-AH hold raw relation references (one per relation type).</t>
         </is>
       </c>
     </row>
@@ -1916,7 +2071,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="55" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>parent_initiative</t>
@@ -1924,7 +2079,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Parent exists, same project, current row isn't Sub-task/Review task, AND parent's type is Milestone/Phase/Risk (i.e. parent is a top-level hierarchy item)</t>
+          <t>Parent exists, same project, current row isn't Sub-task/Review task, AND parent's type is Milestone/Phase/Risk</t>
         </is>
       </c>
       <c r="C5" s="8">
@@ -1933,7 +2088,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Parent Link (Advanced Roadmaps field) — resolves by Issue Key once Pass 0 keys exist</t>
+          <t>Parent Link (Advanced Roadmaps field)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1942,7 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>parent_epic</t>
@@ -1950,17 +2105,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Reserved name for Story→Epic linking. NOTE: this is the gap flagged earlier — no formula here fires for Epic/Feature parents. Needs a real 'Epic Name' lookup formula if Story→Epic linking is in scope.</t>
+          <t>Reserved for Story→Epic linking. Still not implemented — needs a lookup returning the parent's Epic Name, only when parent's type = Epic/Feature</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>NOT YET IMPLEMENTED — VLOOKUP(AB2,$A:$C,3) against the parent row, returning the parent's Subject/Epic Name rather than its ID, only when parent's type = Epic or Feature</t>
+          <t>NOT YET IMPLEMENTED</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Epic Link (Jira Software field) — resolves by Epic NAME, not ID or key</t>
+          <t>Epic Link (Jira Software field) — by NAME, not ID</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1969,7 +2124,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="55" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>parent_subtask</t>
@@ -1986,7 +2141,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Parent Id (Jira Core field) — resolves by numeric ID within same project</t>
+          <t>Parent Id (Jira Core field)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1995,7 +2150,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>parent_same_link</t>
@@ -2003,7 +2158,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Parent exists, same project, current row isn't Sub-task/Review task, AND parent's type is NOT Epic/Feature/Milestone/Phase/Risk (i.e. peer-level relation, not formal hierarchy)</t>
+          <t>Parent exists, same project, current row isn't Sub-task/Review task, AND parent's type is NOT Epic/Feature/Milestone/Phase/Risk</t>
         </is>
       </c>
       <c r="C8" s="8">
@@ -2021,7 +2176,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>is the Child of</t>
@@ -2029,12 +2184,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Catch-all: any row (of any type) whose parent reference didn't resolve into one of the four typed columns above — most commonly cross-project parents</t>
+          <t>Catch-all: parent reference exists but failed the same-project check in the four formulas above — cross-project parents</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Not a formula column in the source — populated by the earlier failed guard clauses (project mismatch) in the four formulas above; consolidate those exclusions into an explicit column if you want it as first-class rather than inferred</t>
+          <t>Inferred from the project-mismatch exclusions above; make it an explicit column if you want it first-class rather than inferred</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -2044,59 +2199,163 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Pass 3, and Pass 4 (cross-project subtasks only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>blocks  (NEW)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Raw blocks reference exists AND target ID exists anywhere in column A — no type restriction, no project restriction (Blocks is commonly cross-project)</t>
-        </is>
-      </c>
-      <c r="C10" s="5">
+          <t>Pass 3, and Pass 4 (cross-project subtasks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>includes</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'includes' reference exists AND target ID exists anywhere in column A — no type/project restriction</t>
+        </is>
+      </c>
+      <c r="C10" s="8">
         <f>IF(AC2="","",IF(ISNA(MATCH(AC2,$A:$A,0)),"",AC2))</f>
         <v/>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Generic Issue Link — 'Blocks' (ID TBD, see Lookup Tables tab)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Pass 5 (NEW — requires ALL rows already imported)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>follows  (NEW)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Raw follows/precedes reference exists AND target ID exists anywhere in column A — no type restriction, no project restriction</t>
-        </is>
-      </c>
-      <c r="C11" s="5">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Includes' (create custom type, or map to 'relates to')</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>blocks</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'blocks' reference exists AND target ID exists anywhere in column A</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
         <f>IF(AD2="","",IF(ISNA(MATCH(AD2,$A:$A,0)),"",AD2))</f>
         <v/>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Generic Issue Link — 'Follows/Precedes' (ID TBD, confirm this link type exists in your instance)</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Pass 5 (NEW — requires ALL rows already imported)</t>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Blocks' (Jira system default)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>relates</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'relates' reference exists AND target ID exists anywhere in column A</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>IF(AE2="","",IF(ISNA(MATCH(AE2,$A:$A,0)),"",AE2))</f>
+        <v/>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Relates' (Jira system default)</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'duplicates' reference exists AND target ID exists anywhere in column A</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>IF(AF2="","",IF(ISNA(MATCH(AF2,$A:$A,0)),"",AF2))</f>
+        <v/>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Duplicates' (Jira system default, symmetric)</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'follows' reference exists AND target ID exists anywhere in column A</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>IF(AG2="","",IF(ISNA(MATCH(AG2,$A:$A,0)),"",AG2))</f>
+        <v/>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Follows/Precedes' (confirm type exists; check vs. requires for duplicate direction)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>requires</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Raw 'requires' reference exists AND target ID exists anywhere in column A</t>
+        </is>
+      </c>
+      <c r="C15" s="8">
+        <f>IF(AH2="","",IF(ISNA(MATCH(AH2,$A:$A,0)),"",AH2))</f>
+        <v/>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Issue Link — 'Requires' (check vs. blocks for duplicate direction before importing both)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Pass 5</t>
         </is>
       </c>
     </row>
